--- a/Project/outputs/tables/table_var_metrics_h22.xlsx
+++ b/Project/outputs/tables/table_var_metrics_h22.xlsx
@@ -482,19 +482,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02685442933250126</v>
+        <v>0.02729135640684522</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08835829112427541</v>
+        <v>0.08583258606380686</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1638732111496606</v>
+        <v>0.165200957645061</v>
       </c>
       <c r="E2" t="n">
-        <v>51.00820530716882</v>
+        <v>47.76353959215616</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4468802698145025</v>
+        <v>0.4401349072512648</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -513,23 +513,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01371679699208656</v>
+        <v>0.01668452492734415</v>
       </c>
       <c r="C3" t="n">
-        <v>0.07070166205069502</v>
+        <v>0.08043883319798703</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1171187303213562</v>
+        <v>0.1291685911022651</v>
       </c>
       <c r="E3" t="n">
-        <v>48.38980074499764</v>
+        <v>45.12430837334296</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4822934232715008</v>
+        <v>0.4789207419898819</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -548,23 +548,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01310120877447539</v>
+        <v>0.01867376364326221</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06770782066241006</v>
+        <v>0.08496831033099934</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1144605118566023</v>
+        <v>0.1366519800195453</v>
       </c>
       <c r="E4" t="n">
-        <v>40.04143389407716</v>
+        <v>48.73938677536155</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5025295109612141</v>
+        <v>0.4806070826306914</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -583,23 +583,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01636718779235321</v>
+        <v>0.01298800007546348</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08060852766034608</v>
+        <v>0.06489179232764601</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1279343104579581</v>
+        <v>0.1139649072103491</v>
       </c>
       <c r="E5" t="n">
-        <v>46.87486803990564</v>
+        <v>36.70390098412967</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5025295109612141</v>
+        <v>0.4957841483979764</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006309923207478145</v>
+        <v>0.006911036980331174</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05380471826620218</v>
+        <v>0.05484388730597587</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07943502506752387</v>
+        <v>0.08313264689838266</v>
       </c>
       <c r="E6" t="n">
-        <v>29.3691557591578</v>
+        <v>30.23409159203631</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4890387858347386</v>
+        <v>0.4856661045531197</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -653,20 +653,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008047508033439066</v>
+        <v>0.01516567079196555</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06348835121020635</v>
+        <v>0.0732724146947743</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0897079039630236</v>
+        <v>0.1231489780386567</v>
       </c>
       <c r="E7" t="n">
-        <v>32.44272987437157</v>
+        <v>39.78350974205047</v>
       </c>
       <c r="F7" t="n">
         <v>0.4991568296795953</v>
@@ -688,23 +688,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02342821061159216</v>
+        <v>0.007936369357555121</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0887093599230581</v>
+        <v>0.06128973285931032</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1530627669016608</v>
+        <v>0.08908630286163592</v>
       </c>
       <c r="E8" t="n">
-        <v>41.21356188806415</v>
+        <v>31.49591899973821</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4957841483979764</v>
+        <v>0.4856661045531197</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -723,23 +723,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006633491019484865</v>
+        <v>0.005507756322745451</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06323265099290158</v>
+        <v>0.05778986734882118</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08144624619640162</v>
+        <v>0.07421425956475919</v>
       </c>
       <c r="E9" t="n">
-        <v>34.55229894366875</v>
+        <v>37.81451237479776</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5126475548060708</v>
+        <v>0.4924114671163575</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01430734447042633</v>
+        <v>0.01389480981318904</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07207642273626184</v>
+        <v>0.07041592801616511</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1158798382392734</v>
+        <v>0.1143210779175819</v>
       </c>
       <c r="E10" t="n">
-        <v>40.48650680642644</v>
+        <v>39.70739605420164</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4913575042158516</v>
+        <v>0.4822934232715008</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.006749645815434301</v>
+        <v>0.006548784406053949</v>
       </c>
       <c r="C11" t="n">
-        <v>0.05974312376297042</v>
+        <v>0.05752790052529596</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08215622809887453</v>
+        <v>0.08092455996824419</v>
       </c>
       <c r="E11" t="n">
-        <v>38.88454315727842</v>
+        <v>36.64938576065769</v>
       </c>
       <c r="F11" t="n">
-        <v>0.4905183312262958</v>
+        <v>0.4771573604060914</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -828,23 +828,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STOXX600</t>
+          <t>DAX</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.004653086958445665</v>
+        <v>0.006413399778718258</v>
       </c>
       <c r="C12" t="n">
-        <v>0.04976813549229007</v>
+        <v>0.05738236823908131</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06821353940711232</v>
+        <v>0.08008370482637686</v>
       </c>
       <c r="E12" t="n">
-        <v>42.43893232561788</v>
+        <v>39.20581573982162</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4968394437420986</v>
+        <v>0.5393401015228426</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -863,23 +863,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FTSE100</t>
+          <t>CAC40</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.004705826350568463</v>
+        <v>0.005947261931555844</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0513792711498461</v>
+        <v>0.05414762553868122</v>
       </c>
       <c r="D13" t="n">
-        <v>0.06859902587186252</v>
+        <v>0.07711849279878234</v>
       </c>
       <c r="E13" t="n">
-        <v>49.87228815660787</v>
+        <v>38.92257907275467</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4993678887484197</v>
+        <v>0.5088832487309645</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -898,23 +898,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DAX</t>
+          <t>FTSE100</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.006081476810567353</v>
+        <v>0.004968035707901342</v>
       </c>
       <c r="C14" t="n">
-        <v>0.05741618715054837</v>
+        <v>0.05131329597261634</v>
       </c>
       <c r="D14" t="n">
-        <v>0.07798382403144484</v>
+        <v>0.0704842940512377</v>
       </c>
       <c r="E14" t="n">
-        <v>40.12941249454982</v>
+        <v>49.85613531279013</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5474083438685209</v>
+        <v>0.4911167512690355</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -937,19 +937,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.01383634755745915</v>
+        <v>0.01369849532232798</v>
       </c>
       <c r="C15" t="n">
-        <v>0.06336606333673563</v>
+        <v>0.06592905954413797</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1176280049880093</v>
+        <v>0.1170405712662407</v>
       </c>
       <c r="E15" t="n">
-        <v>29.00006333020458</v>
+        <v>31.42139914775867</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5246523388116309</v>
+        <v>0.5241116751269036</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -968,23 +968,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HangSeng</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01172649381186748</v>
+        <v>0.006473096992644823</v>
       </c>
       <c r="C16" t="n">
-        <v>0.06685221314661532</v>
+        <v>0.05693625588530293</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1082889367011583</v>
+        <v>0.0804555591158549</v>
       </c>
       <c r="E16" t="n">
-        <v>24.55369106912914</v>
+        <v>33.19430528546452</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5107458912768648</v>
+        <v>0.5088832487309645</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1003,23 +1003,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MSCI_EM</t>
+          <t>HangSeng</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.007509462659279318</v>
+        <v>0.01149598262844626</v>
       </c>
       <c r="C17" t="n">
-        <v>0.06460198703007834</v>
+        <v>0.0661725989896533</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0866571558457772</v>
+        <v>0.1072193202200343</v>
       </c>
       <c r="E17" t="n">
-        <v>40.13052039877363</v>
+        <v>24.45479727699218</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4879898862199747</v>
+        <v>0.516497461928934</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1038,23 +1038,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CSI300</t>
+          <t>SSE</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.004448806237611396</v>
+        <v>0.004968846013885208</v>
       </c>
       <c r="C18" t="n">
-        <v>0.05426646232089362</v>
+        <v>0.05746441057926496</v>
       </c>
       <c r="D18" t="n">
-        <v>0.06669937209308192</v>
+        <v>0.07049004194838593</v>
       </c>
       <c r="E18" t="n">
-        <v>38.60428291616758</v>
+        <v>47.39217126093035</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5221238938053098</v>
+        <v>0.4873096446700508</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.007463893275154141</v>
+        <v>0.007564237847691707</v>
       </c>
       <c r="C19" t="n">
-        <v>0.05842418042374723</v>
+        <v>0.05835918940925425</v>
       </c>
       <c r="D19" t="n">
-        <v>0.08452826087966513</v>
+        <v>0.08547706802439461</v>
       </c>
       <c r="E19" t="n">
-        <v>37.95171673104112</v>
+        <v>37.63707360714623</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5099557522123894</v>
+        <v>0.5066624365482233</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
